--- a/data/_meta/LocalData.xlsx
+++ b/data/_meta/LocalData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D127"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1171,12 +1171,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EnumData.Enum.ArtifactType.1</t>
+          <t>EnumData.Enum.ItemType.11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>스틱</t>
+          <t>마도구 합성 성공 확률 증가</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1185,12 +1185,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>EnumData.Enum.ArtifactType.2</t>
+          <t>EnumData.Enum.ArtifactType.1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>파우더</t>
+          <t>스틱</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1199,12 +1199,12 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EnumData.Enum.ArtifactType.3</t>
+          <t>EnumData.Enum.ArtifactType.2</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>버블건</t>
+          <t>파우더</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1213,12 +1213,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EnumData.Enum.ArtifactType.4</t>
+          <t>EnumData.Enum.ArtifactType.3</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>그라인더</t>
+          <t>버블건</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1227,12 +1227,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EnumData.Enum.ArtifactType.5</t>
+          <t>EnumData.Enum.ArtifactType.4</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>펜던트</t>
+          <t>그라인더</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1241,12 +1241,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000006</t>
+          <t>EnumData.Enum.ArtifactType.5</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>솔라</t>
+          <t>펜던트</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1255,12 +1255,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000006.1</t>
+          <t>ItemData.Item.1000006</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>해가 가장 높이 뜬 정오, 대장장이가 화로에 태양의 기운을 받아 두드려 낸 쇠 동전. 모든 거래의 기준이 되는 화폐로 사용된다.</t>
+          <t>솔라</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1269,12 +1269,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000018</t>
+          <t>ItemData.Item.1000006.1</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>꿈꾸는 별의 스틱</t>
+          <t>해가 가장 높이 뜬 정오, 대장장이가 화로에 태양의 기운을 받아 두드려 낸 쇠 동전. 모든 거래의 기준이 되는 화폐로 사용된다.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1283,12 +1283,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000018.1</t>
+          <t>ItemData.Item.1000018</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>초보 마법소녀 새턴이 「마법소녀 위클리」에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 첫 번째 마도구. 빛나는 토성은 소녀에게 무엇을 보여주게 될까?</t>
+          <t>꿈꾸는 별의 스틱</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1297,12 +1297,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000019</t>
+          <t>ItemData.Item.1000018.1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>꿈꾸는 7색 보석 파우더</t>
+          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 첫 번째 마도구. 빛나는 토성은 소녀에게 무엇을 보여주게 될까?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1311,12 +1311,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000019.2</t>
+          <t>ItemData.Item.1000019</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>초보 마법소녀 새턴이 「마법소녀 위클리」에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 두 번째 마도구. 7색의 보석은 소녀에게 어떤 꿈을 꾸게 해줄까?</t>
+          <t>꿈꾸는 7색 보석 파우더</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1325,12 +1325,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000020</t>
+          <t>ItemData.Item.1000019.2</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>꿈꾸는 윙 버블건</t>
+          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 두 번째 마도구. 7색의 보석은 소녀에게 어떤 꿈을 꾸게 해줄까?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1339,12 +1339,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000020.3</t>
+          <t>ItemData.Item.1000020</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>초보 마법소녀 새턴이 「마법소녀 위클리」에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 세 번째 마도구. 날개 달린 버블건은 소녀를 어디로 데려가줄까?</t>
+          <t>꿈꾸는 윙 버블건</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1353,12 +1353,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000021</t>
+          <t>ItemData.Item.1000020.3</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>그라인더</t>
+          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 세 번째 마도구. 날개 달린 버블건은 소녀를 어디로 데려가줄까?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1367,12 +1367,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000021.4</t>
+          <t>ItemData.Item.1000021</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>「마법소녀 위클리」에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 무엇이든 갈고, 섞고, 흩뿌려보자!</t>
+          <t>그라인더</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1381,12 +1381,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000022</t>
+          <t>ItemData.Item.1000021.4</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>펜던트</t>
+          <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 무엇이든 갈고, 섞고, 흩뿌려보자!</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1395,12 +1395,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000022.5</t>
+          <t>ItemData.Item.1000022</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>「마법소녀 위클리」에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 작지만 단단한 결정이 오래된 소망을 간직하고 있다.</t>
+          <t>펜던트</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1409,12 +1409,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000041</t>
+          <t>ItemData.Item.1000022.5</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>문라이트 베일 파우더</t>
+          <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 작지만 단단한 결정이 오래된 소망을 간직하고 있다.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1423,12 +1423,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000041.6</t>
+          <t>ItemData.Item.1000041</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>아무도 보지 않는 밤, 문라이트 베일 파우더는 더 밝게 빛을 발한다. 무엇으로든 변하고 싶은 마음은 소녀의 힘에 날개를 달아줄 것이다!</t>
+          <t>문라이트 베일 파우더</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1437,12 +1437,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000042</t>
+          <t>ItemData.Item.1000041.6</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>러브문 글로우 파우더</t>
+          <t>아무도 보지 않는 밤, 문라이트 베일 파우더는 더 밝게 빛을 발한다. 무엇으로든 변하고 싶은 마음은 소녀의 힘에 날개를 달아줄 것이다!</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1451,12 +1451,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000042.7</t>
+          <t>ItemData.Item.1000042</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>러브문 글로우 파우더가 마법소녀에게 힘을 더한다. 사랑에 빠진 소녀의 열정을 막을 수 있는 건 아무것도 없지!</t>
+          <t>러브문 글로우 파우더</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1465,12 +1465,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000057</t>
+          <t>ItemData.Item.1000042.7</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>슈가 문 스틱</t>
+          <t>러브문 글로우 파우더가 마법소녀에게 힘을 더한다. 사랑에 빠진 소녀의 열정을 막을 수 있는 건 아무것도 없지!</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1479,12 +1479,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000057.8</t>
+          <t>ItemData.Item.1000057</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>달빛보다 신비롭고 솜사탕보다 달콤한 마법소녀가 당신의 꿈이었다면!</t>
+          <t>슈가 문 스틱</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1493,12 +1493,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000036</t>
+          <t>ItemData.Item.1000057.8</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>미니 끈적이 용액</t>
+          <t>달빛보다 신비롭고 솜사탕보다 달콤한 마법소녀가 당신의 꿈이었다면!</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1507,12 +1507,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000036.1</t>
+          <t>ItemData.Item.1000036</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>슬라임으로 만들어진 귀여운 용량의 끈적이 용액. 이 정도라도 얻을 수 있어 다행이다.</t>
+          <t>미니 끈적이 용액</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1521,12 +1521,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000037</t>
+          <t>ItemData.Item.1000036.1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>포켓 끈적이 용액</t>
+          <t>슬라임으로 만들어진 귀여운 용량의 끈적이 용액. 이 정도라도 얻을 수 있어 다행이다.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1535,12 +1535,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000037.2</t>
+          <t>ItemData.Item.1000037</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>슬라임으로 만들어진 작은 용량의 끈적이 용액. 접착제가 필요할 때 요긴하게 쓰일 수 있을 것이다.</t>
+          <t>포켓 끈적이 용액</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1549,12 +1549,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000038</t>
+          <t>ItemData.Item.1000037.2</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>점보 끈적이 용액</t>
+          <t>슬라임으로 만들어진 작은 용량의 끈적이 용액. 접착제가 필요할 때 요긴하게 쓰일 수 있을 것이다.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1563,12 +1563,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000038.3</t>
+          <t>ItemData.Item.1000038</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>슬라임으로 만들어진 충분한 용량의 끈적이 용액. 접착제 용도로 사용할 수 있다.</t>
+          <t>점보 끈적이 용액</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000039</t>
+          <t>ItemData.Item.1000038.3</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>고급 끈적이 용액</t>
+          <t>슬라임으로 만들어진 충분한 용량의 끈적이 용액. 접착제 용도로 사용할 수 있다.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1591,12 +1591,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000039.4</t>
+          <t>ItemData.Item.1000039</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>고르고 고른 슬라임만으로 뽑아낸 끈적이 용액. 보통 접착제가 '그냥 붙는다'면, 이것은 '티 안 나게 붙는다' 붙인 티가 나지 않는 점이 예술 그 자체.</t>
+          <t>고급 끈적이 용액</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1605,12 +1605,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000058</t>
+          <t>ItemData.Item.1000039.4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>미카의 오로라 파르페</t>
+          <t>고르고 고른 슬라임만으로 뽑아낸 끈적이 용액. 보통 접착제가 '그냥 붙는다'면, 이것은 '티 안 나게 붙는다' 붙인 티가 나지 않는 점이 예술 그 자체.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1619,12 +1619,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000058.5</t>
+          <t>ItemData.Item.1000058</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>솜사탕 가게의 숨겨진 메뉴로 미카의 기분이 내킬 때만 맛볼 수 있는 특제 오로라 파르페. 톡톡 튀는 팝핑캔디와 갖가지 캔디시럽이 내키는 대로 뒤섞인 아름다운 카오스가 황홀경을 맛보여준다고.</t>
+          <t>미카의 오로라 파르페</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1633,12 +1633,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000059</t>
+          <t>ItemData.Item.1000058.5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>미카의 포토카드</t>
+          <t>솜사탕 가게의 숨겨진 메뉴로 미카의 기분이 내킬 때만 맛볼 수 있는 특제 오로라 파르페. 톡톡 튀는 팝핑캔디와 갖가지 캔디시럽이 내키는 대로 뒤섞인 아름다운 카오스가 황홀경을 맛보여준다고.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1647,12 +1647,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000059.6</t>
+          <t>ItemData.Item.1000059</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>아이돌 그룹의 멤버로 활동하던 시절에 소량 제작되었던 미카의 포토카드. 더이상 판매되지 않는 레어템이라 미카의 팬에게는 굉장한 보물일지도?!</t>
+          <t>미카의 포토카드</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1661,12 +1661,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000060</t>
+          <t>ItemData.Item.1000059.6</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>리피파이의 파우더리 캐슬</t>
+          <t>아이돌 그룹의 멤버로 활동하던 시절에 소량 제작되었던 미카의 포토카드. 더이상 판매되지 않는 레어템이라 미카의 팬에게는 굉장한 보물일지도?!</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1675,12 +1675,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000060.7</t>
+          <t>ItemData.Item.1000060</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>리피파이의 손길이 구석구석 닿은 파우더 공예품. 본인은 그저 심심풀이로 만든 잡동사니라지만, 놀라운 섬세함이 눈길을 사로잡는다.</t>
+          <t>리피파이의 파우더리 캐슬</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1689,12 +1689,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000046</t>
+          <t>ItemData.Item.1000060.7</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>핑크 슈가 파우더</t>
+          <t>리피파이의 손길이 구석구석 닿은 파우더 공예품. 본인은 그저 심심풀이로 만든 잡동사니라지만, 놀라운 섬세함이 눈길을 사로잡는다.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1703,12 +1703,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000046.8</t>
+          <t>ItemData.Item.1000046</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>새벽하늘이 잠깐 분홍으로 물드는 그 몇 분을 곱게 빻아 담은 고운 입자의 분홍빛깔의 파우더. 주머니에 매달린 태그에는 흐린 글씨로 '3분의 2만 쓸 것'이라 적혀 있지만, 남은 3분의 1의 쓰임을 아는 사람은 아직 없다.</t>
+          <t>핑크 슈가 파우더</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1717,12 +1717,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000083</t>
+          <t>ItemData.Item.1000046.8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>꿈뭉치</t>
+          <t>새벽하늘이 잠깐 분홍으로 물드는 그 몇 분을 곱게 빻아 담은 고운 입자의 분홍빛깔의 파우더. 주머니에 매달린 태그에는 흐린 글씨로 '3분의 2만 쓸 것'이라 적혀 있지만, 남은 3분의 1의 쓰임을 아는 사람은 아직 없다.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1731,12 +1731,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000083.9</t>
+          <t>ItemData.Item.1000083</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>성실한 솜사탕 베이킹 끝에 얻을 수 있는 작고 신비로운 결정. 달콤한 것을 먹고 행복해진 손님들의 감정이 흘러들어와 마법으로 뭉쳐진 것이라는 설이 있다.</t>
+          <t>꿈뭉치</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1745,12 +1745,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000043</t>
+          <t>ItemData.Item.1000083.9</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>뽀송 프로그 데오도란트</t>
+          <t>성실한 솜사탕 베이킹 끝에 얻을 수 있는 작고 신비로운 결정. 달콤한 것을 먹고 행복해진 손님들의 감정이 흘러들어와 마법으로 뭉쳐진 것이라는 설이 있다.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1759,12 +1759,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000043.1</t>
+          <t>ItemData.Item.1000085</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>이마에 맺힌 땀방울을 확실하게 잡아주는 뽀송 프로그 데오도란트. 기분 좋은 쿨링 효과가 체력을 50 회복시켜준다.</t>
+          <t>하늘색 실타래</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1773,12 +1773,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000044</t>
+          <t>ItemData.Item.1000085.10</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>더스트 펄</t>
+          <t>하늘색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1787,12 +1787,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000044.1</t>
+          <t>ItemData.Item.1000086</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>리피파이가 애정으로 한 알 한 알 손수 뭉친 진주빛 알갱이 펄 파우더. 사역마에게 사용하면 체력을 5 회복시켜준다.</t>
+          <t>파란색 실타래</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1801,12 +1801,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000061</t>
+          <t>ItemData.Item.1000086.11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>사역마 플러피 쿠션</t>
+          <t>파란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1815,12 +1815,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000061.2</t>
+          <t>ItemData.Item.1000087</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>마법 같은 포근함으로 어떤 성실한 사역마도 잠들게 만드는 쿠션. 잠든 사역마는 달콤한 꿈을 꾸며 체력을 100 회복한다.</t>
+          <t>초록색 실타래</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1829,12 +1829,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000062</t>
+          <t>ItemData.Item.1000087.12</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>보송송 목도리</t>
+          <t>초록색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1843,12 +1843,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000062.3</t>
+          <t>ItemData.Item.1000088</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>추운 날씨엔 사역마에게 따스한 목도리를 둘러주자. 찬바람에 소모된 체력을 즉시 100 회복할 수 있다.</t>
+          <t>노란색 실타래</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1857,12 +1857,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000063</t>
+          <t>ItemData.Item.1000088.13</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>사역마용 실키 퍼프</t>
+          <t>노란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1871,12 +1871,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000063.1</t>
+          <t>ItemData.Item.1000089</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>지쳐서 푸석해진 사역마를 순식간에 뽀송하게 되돌려주는 실키 퍼프.</t>
+          <t>주황색 실타래</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1885,12 +1885,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000045</t>
+          <t>ItemData.Item.1000089.14</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>옐로우 허니 파우더</t>
+          <t>주황색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1899,12 +1899,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000045.1</t>
+          <t>ItemData.Item.1000090</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>정오의 햇살이 가장 진하게 고이는 한때를 곱게 빻아 담았다고 하는 노란빛깔의 파우더. 매듭을 풀면 온기가 새어나와 손끝이 먼저 따뜻해진다. 주머니에 매달린 태그에는 흐린 글씨로 '해가 지기 전에 쓸 것'이라 적혀 있지만, 잘 지켜지지 않는다.</t>
+          <t>분홍색 실타래</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1913,12 +1913,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000064</t>
+          <t>ItemData.Item.1000090.15</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>솜솜가루</t>
+          <t>분홍색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1927,12 +1927,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000064.2</t>
+          <t>ItemData.Item.1000091</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>홈베이킹에 쓰이는 가정용 솜사탕 재료. 솜사탕 가게에서 조금씩 얻을 수 있다?</t>
+          <t>보라색 실타래</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1941,12 +1941,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000065</t>
+          <t>ItemData.Item.1000091.16</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>솜솜 열매</t>
+          <t>보라색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1955,12 +1955,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000065.3</t>
+          <t>ItemData.Item.1000092</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>달달한 솜이 폭신하게 열린 솜솜 열매. 잘 심어 가꾸면 더 많은 솜사탕 재료를 얻을 수 있을 것이다.</t>
+          <t>무지개 실타래</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1969,12 +1969,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000066</t>
+          <t>ItemData.Item.1000092.17</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>푸른 꿈결정</t>
+          <t>무지개색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1983,12 +1983,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000066.4</t>
+          <t>ItemData.Item.1000093</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>홈베이킹용 솜솜가루가 달빛을 지나치게 흡수해 파랗게 물든 꿈결정. 때로는 실패가 성공보다 더 아름다운 결과를 가져오는 법이다.</t>
+          <t>포시즌스 별자리 이불</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1997,12 +1997,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000067</t>
+          <t>ItemData.Item.1000093.18</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>솜사타</t>
+          <t>2차 가공 재료. 이불 제작자 하디가 밤하늘의 별자리를 한 땀 한 땀 수놓아 만든 사계절용 최고급 이불. 가벼움과 포근함을 동시에 갖추어 극상의 편안함을 선사하는 이 이불의 마력을 저항할 사람은 적어도 에델크레스트에는 하나도 없을 것이다.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2011,12 +2011,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000067.1</t>
+          <t>ItemData.Item.1000094</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>솜사타에 올라타! 바람처럼 빠르게 데려다줄거야!</t>
+          <t>문라이트 인 헤븐 이불</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2025,12 +2025,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000068</t>
+          <t>ItemData.Item.1000094.19</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>페로페로 향수</t>
+          <t>2차 가공 재료. 극강의 가성비로 에델크레스트 전역에 이름이 높은 이불점의 베스트셀러 상품으로, 거창한 네이밍에는 내돈내산으로 직접 사용해본 고객들의 극찬이 담겨 있다.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2039,12 +2039,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000068.1</t>
+          <t>ItemData.Item.1000095</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>저항할 수 없는 묘한 향기를 풍겨 근처에 있는 사역마를 끌어당기는 미스테리한 향수. 매료된 사역마는 임시 계약을 맺어 하루 동안 당신을 돕는 데에 동의할 것이다.</t>
+          <t>머니캐쳐 누빔 이불</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2053,12 +2053,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000069</t>
+          <t>ItemData.Item.1000095.20</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>솜솜 보틀</t>
+          <t>2차 가공 재료. 이것이 바로 악몽은 물리치고 황금을 불러모은다는 비밀스러운 문양?! 솔라뱅크 객실용으로 납품한다는 것만으로 꽤나 신뢰가 가는데... 솔라뱅크 직원들의 높은 선호도를 보아 캣닢을 잔뜩 뿌려 출고된다는 것도 진실인 것 같다.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2067,12 +2067,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000069.1</t>
+          <t>ItemData.Item.1000096</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>달콤한 솜사탕을 집에서도 만들고 싶다면 솜솜 보틀이 필요할 것이다. 전용 용기가 솜사탕의 달콤함을 오래도록 지켜줄 테니까!</t>
+          <t>노르망디 구스 깃털 한 가닥</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2081,12 +2081,13 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000007</t>
+          <t>ItemData.Item.1000096.21</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>로딩 내용 어쩌고 저쩌고1</t>
+          <t xml:space="preserve">2차 가공 재료. 노르망디 거위에게서 얻은 하늘하늘한 깃털 한 가닥. 오리의 깃털보다 길고 부드럽다.
+이걸 얻는데 </t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2095,12 +2096,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000008</t>
+          <t>ItemData.Item.1000097</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>로딩 내용 어쩌고 저쩌고2</t>
+          <t>페킨 덕 깃털 한 가닥</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2109,12 +2110,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000027</t>
+          <t>ItemData.Item.1000097.22</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>솜사탕상점 로딩화면</t>
+          <t>2차 가공 재료. 페킨 오리에게서 얻은 뽀송뽀송한 깃털 한 가닥. 거위의 깃털보다 짧고 가볍다.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2123,12 +2124,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000028</t>
+          <t>ItemData.Item.1000043</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>파우더상점 로딩화면</t>
+          <t>뽀송 프로그 데오도란트</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -2137,12 +2138,12 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000029</t>
+          <t>ItemData.Item.1000043.1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>이불상점 로딩화면</t>
+          <t>이마에 맺힌 땀방울을 확실하게 잡아주는 뽀송 프로그 데오도란트. 기분 좋은 쿨링 효과가 체력을 50 회복시켜준다.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2151,12 +2152,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MapNpcData.MapNpcMenu.1000009.1</t>
+          <t>ItemData.Item.1000098</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>미니게임 시작</t>
+          <t>라벤더 문 필로우</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2165,12 +2166,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MapNpcData.MapNpcMenu.1000030.1</t>
+          <t>ItemData.Item.1000098.2</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>말걸기</t>
+          <t>라벤더와 캐모마일 허브를 1:1.618의 황금비율로 섞어넣어 마법 같은 휴식을 소환하는 문 필로우의 자세한 제작 방법은 알바생에게도 알려주지 않는 이불점의 일급비밀! 하루에 단 한 번, 다음날의 HP를 +50 추가할 수 있다.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2179,12 +2180,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MapNpcData.MapNpcMenu.1000078.1</t>
+          <t>ItemData.Item.1000099</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>말걸기</t>
+          <t>노르망디 바디필로우</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2193,12 +2194,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MapNpcData.MapStaticNpcMenu.1000031.1</t>
+          <t>ItemData.Item.1000099.3</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>미니게임 시작</t>
+          <t>하얀 노르망디 거위털을 폭신하게 채워넣은 바디필로우. 다음날의 HP를 +10 추가해주는 귀여운 아이템으로, 하루에 세 마리까지만 함께할 수 있다.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2207,16 +2208,506 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MapNpcData.MapStaticNpcMenu.1000084.1</t>
+          <t>ItemData.Item.1000044</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>미니게임 시작</t>
+          <t>더스트 펄</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
       <c r="D127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000044.1</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>리피파이가 애정으로 한 알 한 알 손수 뭉친 진주빛 알갱이 펄 파우더. 사역마에게 사용하면 체력을 5 회복시켜준다.</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000061</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>사역마 플러피 쿠션</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000061.2</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>마법 같은 포근함으로 어떤 성실한 사역마도 잠들게 만드는 쿠션. 잠든 사역마는 달콤한 꿈을 꾸며 체력을 100 회복한다.</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
+      <c r="D130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000062</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>보송송 목도리</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
+      <c r="D131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000062.3</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>추운 날씨엔 사역마에게 따스한 목도리를 둘러주자. 찬바람에 소모된 체력을 즉시 100 회복할 수 있다.</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
+      <c r="D132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000063</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>사역마용 실키 퍼프</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000063.1</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>지쳐서 푸석해진 사역마를 순식간에 뽀송하게 되돌려주는 실키 퍼프.</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr"/>
+      <c r="D134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000045</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>옐로우 허니 파우더</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000045.1</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>정오의 햇살이 가장 진하게 고이는 한때를 곱게 빻아 담았다고 하는 노란빛깔의 파우더. 매듭을 풀면 온기가 새어나와 손끝이 먼저 따뜻해진다. 주머니에 매달린 태그에는 흐린 글씨로 '해가 지기 전에 쓸 것'이라 적혀 있지만, 잘 지켜지지 않는다.</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr"/>
+      <c r="D136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000064</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>솜솜가루</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr"/>
+      <c r="D137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000064.2</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>홈베이킹에 쓰이는 가정용 솜사탕 재료. 솜사탕 가게에서 조금씩 얻을 수 있다?</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000065</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>솜솜 열매</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000065.3</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>달달한 솜이 폭신하게 열린 솜솜 열매. 잘 심어 가꾸면 더 많은 솜사탕 재료를 얻을 수 있을 것이다.</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000066</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>푸른 꿈결정</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr"/>
+      <c r="D141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000066.4</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>홈베이킹용 솜솜가루가 달빛을 지나치게 흡수해 파랗게 물든 꿈결정. 때로는 실패가 성공보다 더 아름다운 결과를 가져오는 법이다.</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000067</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>솜사타</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000067.1</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>솜사타에 올라타! 바람처럼 빠르게 데려다줄거야!</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr"/>
+      <c r="D144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000068</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>페로페로 향수</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr"/>
+      <c r="D145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000068.1</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>저항할 수 없는 묘한 향기를 풍겨 근처에 있는 사역마를 끌어당기는 미스테리한 향수. 매료된 사역마는 임시 계약을 맺어 하루 동안 당신을 돕는 데에 동의할 것이다.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
+      <c r="D146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000069</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>솜솜 보틀</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000069.1</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>달콤한 솜사탕을 집에서도 만들고 싶다면 솜솜 보틀이 필요할 것이다. 전용 용기가 솜사탕의 달콤함을 오래도록 지켜줄 테니까!</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000100</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>굿나잇 아이마스크</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000100.1</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>전설적인 선배 마법소녀들이 남긴 비밀 일지에 따르면, 푹 자고 일어나 맑아진 정신과 반짝이는 눈빛이야말로 마법을 성공시키는 진정한 비결! 마도구 진화 성공 확률을 10프로 높여주는 굿나잇 아이마스크.</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000101</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>폭닥폭닥 수면양말</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000101.2</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>체온을 높여주는 폭닥폭닥한 수면양말로, 마도구 합성 성공 확률을 5프로 높여준다. 한바탕 춤을 춰도 미끄러지지 않도록 내장된 발바닥 패드는 덤. 하루에 다섯 켤레까지 겹쳐서 착용할 수 있다?!</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>LoadingData.Loading.1000007</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>로딩 내용 어쩌고 저쩌고1</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>LoadingData.Loading.1000008</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>로딩 내용 어쩌고 저쩌고2</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>LoadingData.Loading.1000027</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>솜사탕상점 로딩화면</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>LoadingData.Loading.1000028</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>파우더상점 로딩화면</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>LoadingData.Loading.1000029</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>이불상점 로딩화면</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapNpcMenu.1000009.1</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>미니게임 시작</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapNpcMenu.1000030.1</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>말걸기</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapNpcMenu.1000078.1</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>말걸기</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapStaticNpcMenu.1000031.1</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>미니게임 시작</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapStaticNpcMenu.1000084.1</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>미니게임 시작</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/_meta/LocalData.xlsx
+++ b/data/_meta/LocalData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D162"/>
+  <dimension ref="A1:D169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,12 +1255,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000006</t>
+          <t>ItemData.FamiliarCall.1000102</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>솔라</t>
+          <t>노말A형</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1269,12 +1269,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000006.1</t>
+          <t>ItemData.FamiliarCall.1000103</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>해가 가장 높이 뜬 정오, 대장장이가 화로에 태양의 기운을 받아 두드려 낸 쇠 동전. 모든 거래의 기준이 되는 화폐로 사용된다.</t>
+          <t>노말B형</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1283,12 +1283,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000018</t>
+          <t>ItemData.FamiliarCall.1000104</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>꿈꾸는 별의 스틱</t>
+          <t>노말C형</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1297,12 +1297,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000018.1</t>
+          <t>ItemData.Item.1000006</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 첫 번째 마도구. 빛나는 토성은 소녀에게 무엇을 보여주게 될까?</t>
+          <t>솔라</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1311,12 +1311,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000019</t>
+          <t>ItemData.Item.1000006.1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>꿈꾸는 7색 보석 파우더</t>
+          <t>해가 가장 높이 뜬 정오, 대장장이가 화로에 태양의 기운을 받아 두드려 낸 쇠 동전. 모든 거래의 기준이 되는 화폐로 사용된다.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1325,12 +1325,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000019.2</t>
+          <t>ItemData.Item.1000018</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 두 번째 마도구. 7색의 보석은 소녀에게 어떤 꿈을 꾸게 해줄까?</t>
+          <t>꿈꾸는 별의 스틱</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1339,12 +1339,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000020</t>
+          <t>ItemData.Item.1000018.1</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>꿈꾸는 윙 버블건</t>
+          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 첫 번째 마도구. 빛나는 토성은 소녀에게 무엇을 보여주게 될까?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1353,12 +1353,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000020.3</t>
+          <t>ItemData.Item.1000019</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 세 번째 마도구. 날개 달린 버블건은 소녀를 어디로 데려가줄까?</t>
+          <t>꿈꾸는 7색 보석 파우더</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1367,12 +1367,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000021</t>
+          <t>ItemData.Item.1000019.2</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>그라인더</t>
+          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 두 번째 마도구. 7색의 보석은 소녀에게 어떤 꿈을 꾸게 해줄까?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1381,12 +1381,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000021.4</t>
+          <t>ItemData.Item.1000020</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 무엇이든 갈고, 섞고, 흩뿌려보자!</t>
+          <t>꿈꾸는 윙 버블건</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1395,12 +1395,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000022</t>
+          <t>ItemData.Item.1000020.3</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>펜던트</t>
+          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 세 번째 마도구. 날개 달린 버블건은 소녀를 어디로 데려가줄까?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1409,12 +1409,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000022.5</t>
+          <t>ItemData.Item.1000021</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 작지만 단단한 결정이 오래된 소망을 간직하고 있다.</t>
+          <t>그라인더</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1423,12 +1423,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000041</t>
+          <t>ItemData.Item.1000021.4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>문라이트 베일 파우더</t>
+          <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 무엇이든 갈고, 섞고, 흩뿌려보자!</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1437,12 +1437,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000041.6</t>
+          <t>ItemData.Item.1000022</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>아무도 보지 않는 밤, 문라이트 베일 파우더는 더 밝게 빛을 발한다. 무엇으로든 변하고 싶은 마음은 소녀의 힘에 날개를 달아줄 것이다!</t>
+          <t>펜던트</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1451,12 +1451,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000042</t>
+          <t>ItemData.Item.1000022.5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>러브문 글로우 파우더</t>
+          <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 작지만 단단한 결정이 오래된 소망을 간직하고 있다.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1465,12 +1465,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000042.7</t>
+          <t>ItemData.Item.1000041</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>러브문 글로우 파우더가 마법소녀에게 힘을 더한다. 사랑에 빠진 소녀의 열정을 막을 수 있는 건 아무것도 없지!</t>
+          <t>문라이트 베일 파우더</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1479,12 +1479,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000057</t>
+          <t>ItemData.Item.1000041.6</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>슈가 문 스틱</t>
+          <t>아무도 보지 않는 밤, 문라이트 베일 파우더는 더 밝게 빛을 발한다. 무엇으로든 변하고 싶은 마음은 소녀의 힘에 날개를 달아줄 것이다!</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1493,12 +1493,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000057.8</t>
+          <t>ItemData.Item.1000042</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>달빛보다 신비롭고 솜사탕보다 달콤한 마법소녀가 당신의 꿈이었다면!</t>
+          <t>러브문 글로우 파우더</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1507,12 +1507,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000036</t>
+          <t>ItemData.Item.1000042.7</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>미니 끈적이 용액</t>
+          <t>러브문 글로우 파우더가 마법소녀에게 힘을 더한다. 사랑에 빠진 소녀의 열정을 막을 수 있는 건 아무것도 없지!</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1521,12 +1521,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000036.1</t>
+          <t>ItemData.Item.1000057</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>슬라임으로 만들어진 귀여운 용량의 끈적이 용액. 이 정도라도 얻을 수 있어 다행이다.</t>
+          <t>슈가 문 스틱</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1535,12 +1535,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000037</t>
+          <t>ItemData.Item.1000057.8</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>포켓 끈적이 용액</t>
+          <t>달빛보다 신비롭고 솜사탕보다 달콤한 마법소녀가 당신의 꿈이었다면!</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1549,12 +1549,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000037.2</t>
+          <t>ItemData.Item.1000036</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>슬라임으로 만들어진 작은 용량의 끈적이 용액. 접착제가 필요할 때 요긴하게 쓰일 수 있을 것이다.</t>
+          <t>미니 끈적이 용액</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1563,12 +1563,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000038</t>
+          <t>ItemData.Item.1000036.1</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>점보 끈적이 용액</t>
+          <t>슬라임으로 만들어진 귀여운 용량의 끈적이 용액. 이 정도라도 얻을 수 있어 다행이다.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000038.3</t>
+          <t>ItemData.Item.1000037</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>슬라임으로 만들어진 충분한 용량의 끈적이 용액. 접착제 용도로 사용할 수 있다.</t>
+          <t>포켓 끈적이 용액</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1591,12 +1591,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000039</t>
+          <t>ItemData.Item.1000037.2</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>고급 끈적이 용액</t>
+          <t>슬라임으로 만들어진 작은 용량의 끈적이 용액. 접착제가 필요할 때 요긴하게 쓰일 수 있을 것이다.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1605,12 +1605,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000039.4</t>
+          <t>ItemData.Item.1000038</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>고르고 고른 슬라임만으로 뽑아낸 끈적이 용액. 보통 접착제가 '그냥 붙는다'면, 이것은 '티 안 나게 붙는다' 붙인 티가 나지 않는 점이 예술 그 자체.</t>
+          <t>점보 끈적이 용액</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1619,12 +1619,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000058</t>
+          <t>ItemData.Item.1000038.3</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>미카의 오로라 파르페</t>
+          <t>슬라임으로 만들어진 충분한 용량의 끈적이 용액. 접착제 용도로 사용할 수 있다.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1633,12 +1633,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000058.5</t>
+          <t>ItemData.Item.1000039</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>솜사탕 가게의 숨겨진 메뉴로 미카의 기분이 내킬 때만 맛볼 수 있는 특제 오로라 파르페. 톡톡 튀는 팝핑캔디와 갖가지 캔디시럽이 내키는 대로 뒤섞인 아름다운 카오스가 황홀경을 맛보여준다고.</t>
+          <t>고급 끈적이 용액</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1647,12 +1647,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000059</t>
+          <t>ItemData.Item.1000039.4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>미카의 포토카드</t>
+          <t>고르고 고른 슬라임만으로 뽑아낸 끈적이 용액. 보통 접착제가 '그냥 붙는다'면, 이것은 '티 안 나게 붙는다' 붙인 티가 나지 않는 점이 예술 그 자체.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1661,12 +1661,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000059.6</t>
+          <t>ItemData.Item.1000058</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>아이돌 그룹의 멤버로 활동하던 시절에 소량 제작되었던 미카의 포토카드. 더이상 판매되지 않는 레어템이라 미카의 팬에게는 굉장한 보물일지도?!</t>
+          <t>미카의 오로라 파르페</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1675,12 +1675,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000060</t>
+          <t>ItemData.Item.1000058.5</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>리피파이의 파우더리 캐슬</t>
+          <t>솜사탕 가게의 숨겨진 메뉴로 미카의 기분이 내킬 때만 맛볼 수 있는 특제 오로라 파르페. 톡톡 튀는 팝핑캔디와 갖가지 캔디시럽이 내키는 대로 뒤섞인 아름다운 카오스가 황홀경을 맛보여준다고.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1689,12 +1689,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000060.7</t>
+          <t>ItemData.Item.1000059</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>리피파이의 손길이 구석구석 닿은 파우더 공예품. 본인은 그저 심심풀이로 만든 잡동사니라지만, 놀라운 섬세함이 눈길을 사로잡는다.</t>
+          <t>미카의 포토카드</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1703,12 +1703,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000046</t>
+          <t>ItemData.Item.1000059.6</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>핑크 슈가 파우더</t>
+          <t>아이돌 그룹의 멤버로 활동하던 시절에 소량 제작되었던 미카의 포토카드. 더이상 판매되지 않는 레어템이라 미카의 팬에게는 굉장한 보물일지도?!</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1717,12 +1717,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000046.8</t>
+          <t>ItemData.Item.1000060</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>새벽하늘이 잠깐 분홍으로 물드는 그 몇 분을 곱게 빻아 담은 고운 입자의 분홍빛깔의 파우더. 주머니에 매달린 태그에는 흐린 글씨로 '3분의 2만 쓸 것'이라 적혀 있지만, 남은 3분의 1의 쓰임을 아는 사람은 아직 없다.</t>
+          <t>리피파이의 파우더리 캐슬</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1731,12 +1731,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000083</t>
+          <t>ItemData.Item.1000060.7</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>꿈뭉치</t>
+          <t>리피파이의 손길이 구석구석 닿은 파우더 공예품. 본인은 그저 심심풀이로 만든 잡동사니라지만, 놀라운 섬세함이 눈길을 사로잡는다.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1745,12 +1745,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000083.9</t>
+          <t>ItemData.Item.1000046</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>성실한 솜사탕 베이킹 끝에 얻을 수 있는 작고 신비로운 결정. 달콤한 것을 먹고 행복해진 손님들의 감정이 흘러들어와 마법으로 뭉쳐진 것이라는 설이 있다.</t>
+          <t>핑크 슈가 파우더</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1759,12 +1759,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000085</t>
+          <t>ItemData.Item.1000046.8</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>하늘색 실타래</t>
+          <t>새벽하늘이 잠깐 분홍으로 물드는 그 몇 분을 곱게 빻아 담은 고운 입자의 분홍빛깔의 파우더. 주머니에 매달린 태그에는 흐린 글씨로 '3분의 2만 쓸 것'이라 적혀 있지만, 남은 3분의 1의 쓰임을 아는 사람은 아직 없다.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1773,12 +1773,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000085.10</t>
+          <t>ItemData.Item.1000083</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>하늘색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>꿈뭉치</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1787,12 +1787,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000086</t>
+          <t>ItemData.Item.1000083.9</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>파란색 실타래</t>
+          <t>성실한 솜사탕 베이킹 끝에 얻을 수 있는 작고 신비로운 결정. 달콤한 것을 먹고 행복해진 손님들의 감정이 흘러들어와 마법으로 뭉쳐진 것이라는 설이 있다.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1801,12 +1801,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000086.11</t>
+          <t>ItemData.Item.1000085</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>파란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>하늘색 실타래</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1815,12 +1815,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000087</t>
+          <t>ItemData.Item.1000085.10</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>초록색 실타래</t>
+          <t>하늘색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1829,12 +1829,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000087.12</t>
+          <t>ItemData.Item.1000086</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>초록색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>파란색 실타래</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1843,12 +1843,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000088</t>
+          <t>ItemData.Item.1000086.11</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>노란색 실타래</t>
+          <t>파란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1857,12 +1857,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000088.13</t>
+          <t>ItemData.Item.1000087</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>노란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>초록색 실타래</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1871,12 +1871,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000089</t>
+          <t>ItemData.Item.1000087.12</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>주황색 실타래</t>
+          <t>초록색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1885,12 +1885,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000089.14</t>
+          <t>ItemData.Item.1000088</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>주황색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>노란색 실타래</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1899,12 +1899,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000090</t>
+          <t>ItemData.Item.1000088.13</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>분홍색 실타래</t>
+          <t>노란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1913,12 +1913,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000090.15</t>
+          <t>ItemData.Item.1000089</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>분홍색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>주황색 실타래</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1927,12 +1927,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000091</t>
+          <t>ItemData.Item.1000089.14</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>보라색 실타래</t>
+          <t>주황색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1941,12 +1941,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000091.16</t>
+          <t>ItemData.Item.1000090</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>보라색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>분홍색 실타래</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1955,12 +1955,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000092</t>
+          <t>ItemData.Item.1000090.15</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>무지개 실타래</t>
+          <t>분홍색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1969,12 +1969,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000092.17</t>
+          <t>ItemData.Item.1000091</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>무지개색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>보라색 실타래</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1983,12 +1983,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000093</t>
+          <t>ItemData.Item.1000091.16</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>포시즌스 별자리 이불</t>
+          <t>보라색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1997,12 +1997,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000093.18</t>
+          <t>ItemData.Item.1000092</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2차 가공 재료. 이불 제작자 하디가 밤하늘의 별자리를 한 땀 한 땀 수놓아 만든 사계절용 최고급 이불. 가벼움과 포근함을 동시에 갖추어 극상의 편안함을 선사하는 이 이불의 마력을 저항할 사람은 적어도 에델크레스트에는 하나도 없을 것이다.</t>
+          <t>무지개 실타래</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2011,12 +2011,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000094</t>
+          <t>ItemData.Item.1000092.17</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>문라이트 인 헤븐 이불</t>
+          <t>무지개색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2025,12 +2025,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000094.19</t>
+          <t>ItemData.Item.1000093</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2차 가공 재료. 극강의 가성비로 에델크레스트 전역에 이름이 높은 이불점의 베스트셀러 상품으로, 거창한 네이밍에는 내돈내산으로 직접 사용해본 고객들의 극찬이 담겨 있다.</t>
+          <t>포시즌스 별자리 이불</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2039,12 +2039,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000095</t>
+          <t>ItemData.Item.1000093.18</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>머니캐쳐 누빔 이불</t>
+          <t>2차 가공 재료. 이불 제작자 하디가 밤하늘의 별자리를 한 땀 한 땀 수놓아 만든 사계절용 최고급 이불. 가벼움과 포근함을 동시에 갖추어 극상의 편안함을 선사하는 이 이불의 마력을 저항할 사람은 적어도 에델크레스트에는 하나도 없을 것이다.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2053,12 +2053,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000095.20</t>
+          <t>ItemData.Item.1000094</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2차 가공 재료. 이것이 바로 악몽은 물리치고 황금을 불러모은다는 비밀스러운 문양?! 솔라뱅크 객실용으로 납품한다는 것만으로 꽤나 신뢰가 가는데... 솔라뱅크 직원들의 높은 선호도를 보아 캣닢을 잔뜩 뿌려 출고된다는 것도 진실인 것 같다.</t>
+          <t>문라이트 인 헤븐 이불</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2067,12 +2067,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000096</t>
+          <t>ItemData.Item.1000094.19</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>노르망디 구스 깃털 한 가닥</t>
+          <t>2차 가공 재료. 극강의 가성비로 에델크레스트 전역에 이름이 높은 이불점의 베스트셀러 상품으로, 거창한 네이밍에는 내돈내산으로 직접 사용해본 고객들의 극찬이 담겨 있다.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2081,69 +2081,69 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>ItemData.Item.1000095</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>머니캐쳐 누빔 이불</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000095.20</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2차 가공 재료. 이것이 바로 악몽은 물리치고 황금을 불러모은다는 비밀스러운 문양?! 솔라뱅크 객실용으로 납품한다는 것만으로 꽤나 신뢰가 가는데... 솔라뱅크 직원들의 높은 선호도를 보아 캣닢을 잔뜩 뿌려 출고된다는 것도 진실인 것 같다.</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr"/>
+      <c r="D119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>ItemData.Item.1000096</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>노르망디 구스 깃털 한 가닥</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr"/>
+      <c r="D120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
           <t>ItemData.Item.1000096.21</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t xml:space="preserve">2차 가공 재료. 노르망디 거위에게서 얻은 하늘하늘한 깃털 한 가닥. 오리의 깃털보다 길고 부드럽다.
 이걸 얻는데 </t>
         </is>
       </c>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>ItemData.Item.1000097</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>페킨 덕 깃털 한 가닥</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
-      <c r="D119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>ItemData.Item.1000097.22</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>2차 가공 재료. 페킨 오리에게서 얻은 뽀송뽀송한 깃털 한 가닥. 거위의 깃털보다 짧고 가볍다.</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr"/>
-      <c r="D120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>ItemData.Item.1000043</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>뽀송 프로그 데오도란트</t>
-        </is>
-      </c>
       <c r="C121" t="inlineStr"/>
       <c r="D121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000043.1</t>
+          <t>ItemData.Item.1000097</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>이마에 맺힌 땀방울을 확실하게 잡아주는 뽀송 프로그 데오도란트. 기분 좋은 쿨링 효과가 체력을 50 회복시켜준다.</t>
+          <t>페킨 덕 깃털 한 가닥</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -2152,12 +2152,12 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000098</t>
+          <t>ItemData.Item.1000097.22</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>라벤더 문 필로우</t>
+          <t>2차 가공 재료. 페킨 오리에게서 얻은 뽀송뽀송한 깃털 한 가닥. 거위의 깃털보다 짧고 가볍다.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2166,12 +2166,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000098.2</t>
+          <t>ItemData.Item.1000043</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>라벤더와 캐모마일 허브를 1:1.618의 황금비율로 섞어넣어 마법 같은 휴식을 소환하는 문 필로우의 자세한 제작 방법은 알바생에게도 알려주지 않는 이불점의 일급비밀! 하루에 단 한 번, 다음날의 HP를 +50 추가할 수 있다.</t>
+          <t>뽀송 프로그 데오도란트</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2180,12 +2180,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000099</t>
+          <t>ItemData.Item.1000043.1</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>노르망디 바디필로우</t>
+          <t>이마에 맺힌 땀방울을 확실하게 잡아주는 뽀송 프로그 데오도란트. 기분 좋은 쿨링 효과가 체력을 50 회복시켜준다.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2194,12 +2194,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000099.3</t>
+          <t>ItemData.Item.1000098</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>하얀 노르망디 거위털을 폭신하게 채워넣은 바디필로우. 다음날의 HP를 +10 추가해주는 귀여운 아이템으로, 하루에 세 마리까지만 함께할 수 있다.</t>
+          <t>라벤더 문 필로우</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2208,12 +2208,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000044</t>
+          <t>ItemData.Item.1000098.2</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>더스트 펄</t>
+          <t>라벤더와 캐모마일 허브를 1:1.618의 황금비율로 섞어넣어 마법 같은 휴식을 소환하는 문 필로우의 자세한 제작 방법은 알바생에게도 알려주지 않는 이불점의 일급비밀! 하루에 단 한 번, 다음날의 HP를 +50 추가할 수 있다.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -2222,12 +2222,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000044.1</t>
+          <t>ItemData.Item.1000099</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>리피파이가 애정으로 한 알 한 알 손수 뭉친 진주빛 알갱이 펄 파우더. 사역마에게 사용하면 체력을 5 회복시켜준다.</t>
+          <t>노르망디 바디필로우</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -2236,12 +2236,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000061</t>
+          <t>ItemData.Item.1000099.3</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>사역마 플러피 쿠션</t>
+          <t>하얀 노르망디 거위털을 폭신하게 채워넣은 바디필로우. 다음날의 HP를 +10 추가해주는 귀여운 아이템으로, 하루에 세 마리까지만 함께할 수 있다.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -2250,12 +2250,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000061.2</t>
+          <t>ItemData.Item.1000044</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>마법 같은 포근함으로 어떤 성실한 사역마도 잠들게 만드는 쿠션. 잠든 사역마는 달콤한 꿈을 꾸며 체력을 100 회복한다.</t>
+          <t>더스트 펄</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2264,12 +2264,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000062</t>
+          <t>ItemData.Item.1000044.1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>보송송 목도리</t>
+          <t>리피파이가 애정으로 한 알 한 알 손수 뭉친 진주빛 알갱이 펄 파우더. 사역마에게 사용하면 체력을 5 회복시켜준다.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2278,12 +2278,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000062.3</t>
+          <t>ItemData.Item.1000061</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>추운 날씨엔 사역마에게 따스한 목도리를 둘러주자. 찬바람에 소모된 체력을 즉시 100 회복할 수 있다.</t>
+          <t>사역마 플러피 쿠션</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -2292,12 +2292,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000063</t>
+          <t>ItemData.Item.1000061.2</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>사역마용 실키 퍼프</t>
+          <t>마법 같은 포근함으로 어떤 성실한 사역마도 잠들게 만드는 쿠션. 잠든 사역마는 달콤한 꿈을 꾸며 체력을 100 회복한다.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -2306,12 +2306,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000063.1</t>
+          <t>ItemData.Item.1000062</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>지쳐서 푸석해진 사역마를 순식간에 뽀송하게 되돌려주는 실키 퍼프.</t>
+          <t>보송송 목도리</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -2320,12 +2320,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000045</t>
+          <t>ItemData.Item.1000062.3</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>옐로우 허니 파우더</t>
+          <t>추운 날씨엔 사역마에게 따스한 목도리를 둘러주자. 찬바람에 소모된 체력을 즉시 100 회복할 수 있다.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -2334,12 +2334,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000045.1</t>
+          <t>ItemData.Item.1000063</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>정오의 햇살이 가장 진하게 고이는 한때를 곱게 빻아 담았다고 하는 노란빛깔의 파우더. 매듭을 풀면 온기가 새어나와 손끝이 먼저 따뜻해진다. 주머니에 매달린 태그에는 흐린 글씨로 '해가 지기 전에 쓸 것'이라 적혀 있지만, 잘 지켜지지 않는다.</t>
+          <t>사역마용 실키 퍼프</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -2348,12 +2348,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000064</t>
+          <t>ItemData.Item.1000063.1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>솜솜가루</t>
+          <t>지쳐서 푸석해진 사역마를 순식간에 뽀송하게 되돌려주는 실키 퍼프.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -2362,12 +2362,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000064.2</t>
+          <t>ItemData.Item.1000045</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>홈베이킹에 쓰이는 가정용 솜사탕 재료. 솜사탕 가게에서 조금씩 얻을 수 있다?</t>
+          <t>옐로우 허니 파우더</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -2376,12 +2376,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000065</t>
+          <t>ItemData.Item.1000045.1</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>솜솜 열매</t>
+          <t>정오의 햇살이 가장 진하게 고이는 한때를 곱게 빻아 담았다고 하는 노란빛깔의 파우더. 매듭을 풀면 온기가 새어나와 손끝이 먼저 따뜻해진다. 주머니에 매달린 태그에는 흐린 글씨로 '해가 지기 전에 쓸 것'이라 적혀 있지만, 잘 지켜지지 않는다.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -2390,12 +2390,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000065.3</t>
+          <t>ItemData.Item.1000064</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>달달한 솜이 폭신하게 열린 솜솜 열매. 잘 심어 가꾸면 더 많은 솜사탕 재료를 얻을 수 있을 것이다.</t>
+          <t>솜솜가루</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -2404,12 +2404,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000066</t>
+          <t>ItemData.Item.1000064.2</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>푸른 꿈결정</t>
+          <t>홈베이킹에 쓰이는 가정용 솜사탕 재료. 솜사탕 가게에서 조금씩 얻을 수 있다?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2418,12 +2418,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000066.4</t>
+          <t>ItemData.Item.1000065</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>홈베이킹용 솜솜가루가 달빛을 지나치게 흡수해 파랗게 물든 꿈결정. 때로는 실패가 성공보다 더 아름다운 결과를 가져오는 법이다.</t>
+          <t>솜솜 열매</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2432,12 +2432,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000067</t>
+          <t>ItemData.Item.1000065.3</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>솜사타</t>
+          <t>달달한 솜이 폭신하게 열린 솜솜 열매. 잘 심어 가꾸면 더 많은 솜사탕 재료를 얻을 수 있을 것이다.</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2446,12 +2446,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000067.1</t>
+          <t>ItemData.Item.1000066</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>솜사타에 올라타! 바람처럼 빠르게 데려다줄거야!</t>
+          <t>푸른 꿈결정</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2460,12 +2460,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000068</t>
+          <t>ItemData.Item.1000066.4</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>페로페로 향수</t>
+          <t>홈베이킹용 솜솜가루가 달빛을 지나치게 흡수해 파랗게 물든 꿈결정. 때로는 실패가 성공보다 더 아름다운 결과를 가져오는 법이다.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2474,12 +2474,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000068.1</t>
+          <t>ItemData.Item.1000067</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>저항할 수 없는 묘한 향기를 풍겨 근처에 있는 사역마를 끌어당기는 미스테리한 향수. 매료된 사역마는 임시 계약을 맺어 하루 동안 당신을 돕는 데에 동의할 것이다.</t>
+          <t>솜사타</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2488,12 +2488,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000069</t>
+          <t>ItemData.Item.1000067.1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>솜솜 보틀</t>
+          <t>솜사타에 올라타! 바람처럼 빠르게 데려다줄거야!</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2502,12 +2502,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000069.1</t>
+          <t>ItemData.Item.1000102</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>달콤한 솜사탕을 집에서도 만들고 싶다면 솜솜 보틀이 필요할 것이다. 전용 용기가 솜사탕의 달콤함을 오래도록 지켜줄 테니까!</t>
+          <t>페로페로 향수</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2516,12 +2516,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000100</t>
+          <t>ItemData.Item.1000102.1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>굿나잇 아이마스크</t>
+          <t>저항할 수 없는 묘한 향기를 풍겨 근처에 있는 사역마를 끌어당기는 미스테리한 향수. 매료된 사역마는 임시 계약을 맺어 하루 동안 당신을 돕는 데에 동의할 것이다.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2530,12 +2530,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000100.1</t>
+          <t>ItemData.Item.1000103</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>전설적인 선배 마법소녀들이 남긴 비밀 일지에 따르면, 푹 자고 일어나 맑아진 정신과 반짝이는 눈빛이야말로 마법을 성공시키는 진정한 비결! 마도구 진화 성공 확률을 10프로 높여주는 굿나잇 아이마스크.</t>
+          <t>페로페로 향수</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2544,12 +2544,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000101</t>
+          <t>ItemData.Item.1000103.2</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>폭닥폭닥 수면양말</t>
+          <t>저항할 수 없는 묘한 향기를 풍겨 근처에 있는 사역마를 끌어당기는 미스테리한 향수. 매료된 사역마는 임시 계약을 맺어 하루 동안 당신을 돕는 데에 동의할 것이다.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2558,12 +2558,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000101.2</t>
+          <t>ItemData.Item.1000104</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>체온을 높여주는 폭닥폭닥한 수면양말로, 마도구 합성 성공 확률을 5프로 높여준다. 한바탕 춤을 춰도 미끄러지지 않도록 내장된 발바닥 패드는 덤. 하루에 다섯 켤레까지 겹쳐서 착용할 수 있다?!</t>
+          <t>페로페로 향수</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2572,12 +2572,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000007</t>
+          <t>ItemData.Item.1000104.3</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>로딩 내용 어쩌고 저쩌고1</t>
+          <t>저항할 수 없는 묘한 향기를 풍겨 근처에 있는 사역마를 끌어당기는 미스테리한 향수. 매료된 사역마는 임시 계약을 맺어 하루 동안 당신을 돕는 데에 동의할 것이다.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2586,12 +2586,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000008</t>
+          <t>ItemData.Item.1000069</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>로딩 내용 어쩌고 저쩌고2</t>
+          <t>솜솜 보틀</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2600,12 +2600,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000027</t>
+          <t>ItemData.Item.1000069.1</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>솜사탕상점 로딩화면</t>
+          <t>달콤한 솜사탕을 집에서도 만들고 싶다면 솜솜 보틀이 필요할 것이다. 전용 용기가 솜사탕의 달콤함을 오래도록 지켜줄 테니까!</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2614,12 +2614,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000028</t>
+          <t>ItemData.Item.1000100</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>파우더상점 로딩화면</t>
+          <t>굿나잇 아이마스크</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2628,12 +2628,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000029</t>
+          <t>ItemData.Item.1000100.1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>이불상점 로딩화면</t>
+          <t>전설적인 선배 마법소녀들이 남긴 비밀 일지에 따르면, 푹 자고 일어나 맑아진 정신과 반짝이는 눈빛이야말로 마법을 성공시키는 진정한 비결! 마도구 진화 성공 확률을 10프로 높여주는 굿나잇 아이마스크.</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2642,12 +2642,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>MapNpcData.MapNpcMenu.1000009.1</t>
+          <t>ItemData.Item.1000101</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>미니게임 시작</t>
+          <t>폭닥폭닥 수면양말</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2656,12 +2656,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>MapNpcData.MapNpcMenu.1000030.1</t>
+          <t>ItemData.Item.1000101.2</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>말걸기</t>
+          <t>체온을 높여주는 폭닥폭닥한 수면양말로, 마도구 합성 성공 확률을 5프로 높여준다. 한바탕 춤을 춰도 미끄러지지 않도록 내장된 발바닥 패드는 덤. 하루에 다섯 켤레까지 겹쳐서 착용할 수 있다?!</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2670,12 +2670,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>MapNpcData.MapNpcMenu.1000078.1</t>
+          <t>LoadingData.Loading.1000007</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>말걸기</t>
+          <t>로딩 내용 어쩌고 저쩌고1</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2684,12 +2684,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>MapNpcData.MapStaticNpcMenu.1000031.1</t>
+          <t>LoadingData.Loading.1000008</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>미니게임 시작</t>
+          <t>로딩 내용 어쩌고 저쩌고2</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2698,16 +2698,114 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>MapNpcData.MapStaticNpcMenu.1000084.1</t>
+          <t>LoadingData.Loading.1000027</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>미니게임 시작</t>
+          <t>솜사탕상점 로딩화면</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>LoadingData.Loading.1000028</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>파우더상점 로딩화면</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>LoadingData.Loading.1000029</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>이불상점 로딩화면</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapNpcMenu.1000009.1</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>미니게임 시작</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapNpcMenu.1000030.1</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>말걸기</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapNpcMenu.1000078.1</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>말걸기</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapStaticNpcMenu.1000031.1</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>미니게임 시작</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapStaticNpcMenu.1000084.1</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>미니게임 시작</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/_meta/LocalData.xlsx
+++ b/data/_meta/LocalData.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D169"/>
+  <dimension ref="A1:D172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1255,7 +1255,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ItemData.FamiliarCall.1000102</t>
+          <t>ItemData.FamiliarCall.1000068</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -1269,12 +1269,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ItemData.FamiliarCall.1000103</t>
+          <t>ItemData.FamiliarCall.1000108</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>노말B형</t>
+          <t>에픽A형</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1283,12 +1283,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ItemData.FamiliarCall.1000104</t>
+          <t>ItemData.FamiliarCall.1000109</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>노말C형</t>
+          <t>에픽B형</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1297,12 +1297,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000006</t>
+          <t>ItemData.FamiliarCall.1000110</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>솔라</t>
+          <t>에픽C형</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1311,12 +1311,12 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000006.1</t>
+          <t>ItemData.Item.1000006</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>해가 가장 높이 뜬 정오, 대장장이가 화로에 태양의 기운을 받아 두드려 낸 쇠 동전. 모든 거래의 기준이 되는 화폐로 사용된다.</t>
+          <t>솔라</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1325,12 +1325,12 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000018</t>
+          <t>ItemData.Item.1000006.1</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>꿈꾸는 별의 스틱</t>
+          <t>해가 가장 높이 뜬 정오, 대장장이가 화로에 태양의 기운을 받아 두드려 낸 쇠 동전. 모든 거래의 기준이 되는 화폐로 사용된다.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1339,12 +1339,12 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000018.1</t>
+          <t>ItemData.Item.1000018</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 첫 번째 마도구. 빛나는 토성은 소녀에게 무엇을 보여주게 될까?</t>
+          <t>꿈꾸는 별의 스틱</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1353,12 +1353,12 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000019</t>
+          <t>ItemData.Item.1000018.1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>꿈꾸는 7색 보석 파우더</t>
+          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 첫 번째 마도구. 빛나는 토성은 소녀에게 무엇을 보여주게 될까?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1367,12 +1367,12 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000019.2</t>
+          <t>ItemData.Item.1000019</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 두 번째 마도구. 7색의 보석은 소녀에게 어떤 꿈을 꾸게 해줄까?</t>
+          <t>꿈꾸는 7색 보석 파우더</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1381,12 +1381,12 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000020</t>
+          <t>ItemData.Item.1000019.2</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>꿈꾸는 윙 버블건</t>
+          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 두 번째 마도구. 7색의 보석은 소녀에게 어떤 꿈을 꾸게 해줄까?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1395,12 +1395,12 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000020.3</t>
+          <t>ItemData.Item.1000020</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 세 번째 마도구. 날개 달린 버블건은 소녀를 어디로 데려가줄까?</t>
+          <t>꿈꾸는 윙 버블건</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1409,12 +1409,12 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000021</t>
+          <t>ItemData.Item.1000020.3</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>그라인더</t>
+          <t>초보 마법소녀 새턴이 '마법소녀 위클리'에서 주문한  '소녀의 꿈, 핑크 아티팩트 3종 세트'의 세 번째 마도구. 날개 달린 버블건은 소녀를 어디로 데려가줄까?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1423,12 +1423,12 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000021.4</t>
+          <t>ItemData.Item.1000021</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 무엇이든 갈고, 섞고, 흩뿌려보자!</t>
+          <t>그라인더</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1437,12 +1437,12 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000022</t>
+          <t>ItemData.Item.1000021.4</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>펜던트</t>
+          <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 무엇이든 갈고, 섞고, 흩뿌려보자!</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1451,12 +1451,12 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000022.5</t>
+          <t>ItemData.Item.1000022</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 작지만 단단한 결정이 오래된 소망을 간직하고 있다.</t>
+          <t>펜던트</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1465,12 +1465,12 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000041</t>
+          <t>ItemData.Item.1000022.5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>문라이트 베일 파우더</t>
+          <t>마법소녀 위클리'에서 주문할 수 있는  '소녀의 꿈, 핑크 아티팩트 추가 2종 세트'의 마도구. 작지만 단단한 결정이 오래된 소망을 간직하고 있다.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1479,12 +1479,12 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000041.6</t>
+          <t>ItemData.Item.1000041</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>아무도 보지 않는 밤, 문라이트 베일 파우더는 더 밝게 빛을 발한다. 무엇으로든 변하고 싶은 마음은 소녀의 힘에 날개를 달아줄 것이다!</t>
+          <t>문라이트 베일 파우더</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1493,12 +1493,12 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000042</t>
+          <t>ItemData.Item.1000041.6</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>러브문 글로우 파우더</t>
+          <t>아무도 보지 않는 밤, 문라이트 베일 파우더는 더 밝게 빛을 발한다. 무엇으로든 변하고 싶은 마음은 소녀의 힘에 날개를 달아줄 것이다!</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1507,12 +1507,12 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000042.7</t>
+          <t>ItemData.Item.1000042</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>러브문 글로우 파우더가 마법소녀에게 힘을 더한다. 사랑에 빠진 소녀의 열정을 막을 수 있는 건 아무것도 없지!</t>
+          <t>러브문 글로우 파우더</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1521,12 +1521,12 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000057</t>
+          <t>ItemData.Item.1000042.7</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>슈가 문 스틱</t>
+          <t>러브문 글로우 파우더가 마법소녀에게 힘을 더한다. 사랑에 빠진 소녀의 열정을 막을 수 있는 건 아무것도 없지!</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1535,12 +1535,12 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000057.8</t>
+          <t>ItemData.Item.1000057</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>달빛보다 신비롭고 솜사탕보다 달콤한 마법소녀가 당신의 꿈이었다면!</t>
+          <t>슈가 문 스틱</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1549,12 +1549,12 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000036</t>
+          <t>ItemData.Item.1000057.8</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>미니 끈적이 용액</t>
+          <t>달빛보다 신비롭고 솜사탕보다 달콤한 마법소녀가 당신의 꿈이었다면!</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1563,12 +1563,12 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000036.1</t>
+          <t>ItemData.Item.1000036</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>슬라임으로 만들어진 귀여운 용량의 끈적이 용액. 이 정도라도 얻을 수 있어 다행이다.</t>
+          <t>미니 끈적이 용액</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1577,12 +1577,12 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000037</t>
+          <t>ItemData.Item.1000036.1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>포켓 끈적이 용액</t>
+          <t>슬라임으로 만들어진 귀여운 용량의 끈적이 용액. 이 정도라도 얻을 수 있어 다행이다.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1591,12 +1591,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000037.2</t>
+          <t>ItemData.Item.1000037</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>슬라임으로 만들어진 작은 용량의 끈적이 용액. 접착제가 필요할 때 요긴하게 쓰일 수 있을 것이다.</t>
+          <t>포켓 끈적이 용액</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1605,12 +1605,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000038</t>
+          <t>ItemData.Item.1000037.2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>점보 끈적이 용액</t>
+          <t>슬라임으로 만들어진 작은 용량의 끈적이 용액. 접착제가 필요할 때 요긴하게 쓰일 수 있을 것이다.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1619,12 +1619,12 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000038.3</t>
+          <t>ItemData.Item.1000038</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>슬라임으로 만들어진 충분한 용량의 끈적이 용액. 접착제 용도로 사용할 수 있다.</t>
+          <t>점보 끈적이 용액</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1633,12 +1633,12 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000039</t>
+          <t>ItemData.Item.1000038.3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>고급 끈적이 용액</t>
+          <t>슬라임으로 만들어진 충분한 용량의 끈적이 용액. 접착제 용도로 사용할 수 있다.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1647,12 +1647,12 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000039.4</t>
+          <t>ItemData.Item.1000039</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>고르고 고른 슬라임만으로 뽑아낸 끈적이 용액. 보통 접착제가 '그냥 붙는다'면, 이것은 '티 안 나게 붙는다' 붙인 티가 나지 않는 점이 예술 그 자체.</t>
+          <t>고급 끈적이 용액</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1661,12 +1661,12 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000058</t>
+          <t>ItemData.Item.1000039.4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>미카의 오로라 파르페</t>
+          <t>고르고 고른 슬라임만으로 뽑아낸 끈적이 용액. 보통 접착제가 '그냥 붙는다'면, 이것은 '티 안 나게 붙는다' 붙인 티가 나지 않는 점이 예술 그 자체.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1675,12 +1675,12 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000058.5</t>
+          <t>ItemData.Item.1000058</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>솜사탕 가게의 숨겨진 메뉴로 미카의 기분이 내킬 때만 맛볼 수 있는 특제 오로라 파르페. 톡톡 튀는 팝핑캔디와 갖가지 캔디시럽이 내키는 대로 뒤섞인 아름다운 카오스가 황홀경을 맛보여준다고.</t>
+          <t>미카의 오로라 파르페</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1689,12 +1689,12 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000059</t>
+          <t>ItemData.Item.1000058.5</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>미카의 포토카드</t>
+          <t>솜사탕 가게의 숨겨진 메뉴로 미카의 기분이 내킬 때만 맛볼 수 있는 특제 오로라 파르페. 톡톡 튀는 팝핑캔디와 갖가지 캔디시럽이 내키는 대로 뒤섞인 아름다운 카오스가 황홀경을 맛보여준다고.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1703,12 +1703,12 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000059.6</t>
+          <t>ItemData.Item.1000059</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>아이돌 그룹의 멤버로 활동하던 시절에 소량 제작되었던 미카의 포토카드. 더이상 판매되지 않는 레어템이라 미카의 팬에게는 굉장한 보물일지도?!</t>
+          <t>미카의 포토카드</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1717,12 +1717,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000060</t>
+          <t>ItemData.Item.1000059.6</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>리피파이의 파우더리 캐슬</t>
+          <t>아이돌 그룹의 멤버로 활동하던 시절에 소량 제작되었던 미카의 포토카드. 더이상 판매되지 않는 레어템이라 미카의 팬에게는 굉장한 보물일지도?!</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1731,12 +1731,12 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000060.7</t>
+          <t>ItemData.Item.1000060</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>리피파이의 손길이 구석구석 닿은 파우더 공예품. 본인은 그저 심심풀이로 만든 잡동사니라지만, 놀라운 섬세함이 눈길을 사로잡는다.</t>
+          <t>리피파이의 파우더리 캐슬</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1745,12 +1745,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000046</t>
+          <t>ItemData.Item.1000060.7</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>핑크 슈가 파우더</t>
+          <t>리피파이의 손길이 구석구석 닿은 파우더 공예품. 본인은 그저 심심풀이로 만든 잡동사니라지만, 놀라운 섬세함이 눈길을 사로잡는다.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1759,12 +1759,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000046.8</t>
+          <t>ItemData.Item.1000046</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>새벽하늘이 잠깐 분홍으로 물드는 그 몇 분을 곱게 빻아 담은 고운 입자의 분홍빛깔의 파우더. 주머니에 매달린 태그에는 흐린 글씨로 '3분의 2만 쓸 것'이라 적혀 있지만, 남은 3분의 1의 쓰임을 아는 사람은 아직 없다.</t>
+          <t>핑크 슈가 파우더</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1773,12 +1773,12 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000083</t>
+          <t>ItemData.Item.1000046.8</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>꿈뭉치</t>
+          <t>새벽하늘이 잠깐 분홍으로 물드는 그 몇 분을 곱게 빻아 담은 고운 입자의 분홍빛깔의 파우더. 주머니에 매달린 태그에는 흐린 글씨로 '3분의 2만 쓸 것'이라 적혀 있지만, 남은 3분의 1의 쓰임을 아는 사람은 아직 없다.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1787,12 +1787,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000083.9</t>
+          <t>ItemData.Item.1000083</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>성실한 솜사탕 베이킹 끝에 얻을 수 있는 작고 신비로운 결정. 달콤한 것을 먹고 행복해진 손님들의 감정이 흘러들어와 마법으로 뭉쳐진 것이라는 설이 있다.</t>
+          <t>꿈뭉치</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1801,12 +1801,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000085</t>
+          <t>ItemData.Item.1000083.9</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>하늘색 실타래</t>
+          <t>성실한 솜사탕 베이킹 끝에 얻을 수 있는 작고 신비로운 결정. 달콤한 것을 먹고 행복해진 손님들의 감정이 흘러들어와 마법으로 뭉쳐진 것이라는 설이 있다.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1815,12 +1815,12 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000085.10</t>
+          <t>ItemData.Item.1000085</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>하늘색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>하늘색 실타래</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1829,12 +1829,12 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000086</t>
+          <t>ItemData.Item.1000085.10</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>파란색 실타래</t>
+          <t>하늘색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1843,12 +1843,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000086.11</t>
+          <t>ItemData.Item.1000086</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>파란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>파란색 실타래</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1857,12 +1857,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000087</t>
+          <t>ItemData.Item.1000086.11</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>초록색 실타래</t>
+          <t>파란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1871,12 +1871,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000087.12</t>
+          <t>ItemData.Item.1000087</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>초록색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>초록색 실타래</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1885,12 +1885,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000088</t>
+          <t>ItemData.Item.1000087.12</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>노란색 실타래</t>
+          <t>초록색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1899,12 +1899,12 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000088.13</t>
+          <t>ItemData.Item.1000088</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>노란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>노란색 실타래</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1913,12 +1913,12 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000089</t>
+          <t>ItemData.Item.1000088.13</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>주황색 실타래</t>
+          <t>노란색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1927,12 +1927,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000089.14</t>
+          <t>ItemData.Item.1000089</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>주황색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>주황색 실타래</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1941,12 +1941,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000090</t>
+          <t>ItemData.Item.1000089.14</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>분홍색 실타래</t>
+          <t>주황색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1955,12 +1955,12 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000090.15</t>
+          <t>ItemData.Item.1000090</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>분홍색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>분홍색 실타래</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1969,12 +1969,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000091</t>
+          <t>ItemData.Item.1000090.15</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>보라색 실타래</t>
+          <t>분홍색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1983,12 +1983,12 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000091.16</t>
+          <t>ItemData.Item.1000091</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>보라색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>보라색 실타래</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1997,12 +1997,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000092</t>
+          <t>ItemData.Item.1000091.16</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>무지개 실타래</t>
+          <t>보라색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -2011,12 +2011,12 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000092.17</t>
+          <t>ItemData.Item.1000092</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>무지개색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
+          <t>무지개 실타래</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -2025,12 +2025,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000093</t>
+          <t>ItemData.Item.1000092.17</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>포시즌스 별자리 이불</t>
+          <t>무지개색 실이 동그랗게 뭉쳐진 양질의 실타래. 이것으로 바느질하면 갖가지 물건을 만들 수 있는데, 고양이 집사들에게만 보이는 다른 용도도 있다.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -2039,12 +2039,12 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000093.18</t>
+          <t>ItemData.Item.1000093</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2차 가공 재료. 이불 제작자 하디가 밤하늘의 별자리를 한 땀 한 땀 수놓아 만든 사계절용 최고급 이불. 가벼움과 포근함을 동시에 갖추어 극상의 편안함을 선사하는 이 이불의 마력을 저항할 사람은 적어도 에델크레스트에는 하나도 없을 것이다.</t>
+          <t>포시즌스 별자리 이불</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -2053,12 +2053,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000094</t>
+          <t>ItemData.Item.1000093.18</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>문라이트 인 헤븐 이불</t>
+          <t>2차 가공 재료. 이불 제작자 하디가 밤하늘의 별자리를 한 땀 한 땀 수놓아 만든 사계절용 최고급 이불. 가벼움과 포근함을 동시에 갖추어 극상의 편안함을 선사하는 이 이불의 마력을 저항할 사람은 적어도 에델크레스트에는 하나도 없을 것이다.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -2067,12 +2067,12 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000094.19</t>
+          <t>ItemData.Item.1000094</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2차 가공 재료. 극강의 가성비로 에델크레스트 전역에 이름이 높은 이불점의 베스트셀러 상품으로, 거창한 네이밍에는 내돈내산으로 직접 사용해본 고객들의 극찬이 담겨 있다.</t>
+          <t>문라이트 인 헤븐 이불</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -2081,12 +2081,12 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000095</t>
+          <t>ItemData.Item.1000094.19</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>머니캐쳐 누빔 이불</t>
+          <t>2차 가공 재료. 극강의 가성비로 에델크레스트 전역에 이름이 높은 이불점의 베스트셀러 상품으로, 거창한 네이밍에는 내돈내산으로 직접 사용해본 고객들의 극찬이 담겨 있다.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -2095,12 +2095,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000095.20</t>
+          <t>ItemData.Item.1000095</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2차 가공 재료. 이것이 바로 악몽은 물리치고 황금을 불러모은다는 비밀스러운 문양?! 솔라뱅크 객실용으로 납품한다는 것만으로 꽤나 신뢰가 가는데... 솔라뱅크 직원들의 높은 선호도를 보아 캣닢을 잔뜩 뿌려 출고된다는 것도 진실인 것 같다.</t>
+          <t>머니캐쳐 누빔 이불</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -2109,12 +2109,12 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000096</t>
+          <t>ItemData.Item.1000095.20</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>노르망디 구스 깃털 한 가닥</t>
+          <t>2차 가공 재료. 이것이 바로 악몽은 물리치고 황금을 불러모은다는 비밀스러운 문양?! 솔라뱅크 객실용으로 납품한다는 것만으로 꽤나 신뢰가 가는데... 솔라뱅크 직원들의 높은 선호도를 보아 캣닢을 잔뜩 뿌려 출고된다는 것도 진실인 것 같다.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -2123,41 +2123,41 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>ItemData.Item.1000096</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>노르망디 구스 깃털 한 가닥</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr"/>
+      <c r="D121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>ItemData.Item.1000096.21</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t xml:space="preserve">2차 가공 재료. 노르망디 거위에게서 얻은 하늘하늘한 깃털 한 가닥. 오리의 깃털보다 길고 부드럽다.
 이걸 얻는데 </t>
         </is>
       </c>
-      <c r="C121" t="inlineStr"/>
-      <c r="D121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>ItemData.Item.1000097</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>페킨 덕 깃털 한 가닥</t>
-        </is>
-      </c>
       <c r="C122" t="inlineStr"/>
       <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000097.22</t>
+          <t>ItemData.Item.1000097</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2차 가공 재료. 페킨 오리에게서 얻은 뽀송뽀송한 깃털 한 가닥. 거위의 깃털보다 짧고 가볍다.</t>
+          <t>페킨 덕 깃털 한 가닥</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -2166,12 +2166,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000043</t>
+          <t>ItemData.Item.1000097.22</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>뽀송 프로그 데오도란트</t>
+          <t>2차 가공 재료. 페킨 오리에게서 얻은 뽀송뽀송한 깃털 한 가닥. 거위의 깃털보다 짧고 가볍다.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -2180,12 +2180,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000043.1</t>
+          <t>ItemData.Item.1000043</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>이마에 맺힌 땀방울을 확실하게 잡아주는 뽀송 프로그 데오도란트. 기분 좋은 쿨링 효과가 체력을 50 회복시켜준다.</t>
+          <t>뽀송 프로그 데오도란트</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -2194,12 +2194,12 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000098</t>
+          <t>ItemData.Item.1000043.1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>라벤더 문 필로우</t>
+          <t>이마에 맺힌 땀방울을 확실하게 잡아주는 뽀송 프로그 데오도란트. 기분 좋은 쿨링 효과가 체력을 50 회복시켜준다.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -2208,12 +2208,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000098.2</t>
+          <t>ItemData.Item.1000098</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>라벤더와 캐모마일 허브를 1:1.618의 황금비율로 섞어넣어 마법 같은 휴식을 소환하는 문 필로우의 자세한 제작 방법은 알바생에게도 알려주지 않는 이불점의 일급비밀! 하루에 단 한 번, 다음날의 HP를 +50 추가할 수 있다.</t>
+          <t>라벤더 문 필로우</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -2222,12 +2222,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000099</t>
+          <t>ItemData.Item.1000098.2</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>노르망디 바디필로우</t>
+          <t>라벤더와 캐모마일 허브를 1:1.618의 황금비율로 섞어넣어 마법 같은 휴식을 소환하는 문 필로우의 자세한 제작 방법은 알바생에게도 알려주지 않는 이불점의 일급비밀! 하루에 단 한 번, 다음날의 HP를 +50 추가할 수 있다.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -2236,12 +2236,12 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000099.3</t>
+          <t>ItemData.Item.1000099</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>하얀 노르망디 거위털을 폭신하게 채워넣은 바디필로우. 다음날의 HP를 +10 추가해주는 귀여운 아이템으로, 하루에 세 마리까지만 함께할 수 있다.</t>
+          <t>노르망디 바디필로우</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -2250,12 +2250,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000044</t>
+          <t>ItemData.Item.1000099.3</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>더스트 펄</t>
+          <t>하얀 노르망디 거위털을 폭신하게 채워넣은 바디필로우. 다음날의 HP를 +10 추가해주는 귀여운 아이템으로, 하루에 세 마리까지만 함께할 수 있다.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -2264,12 +2264,12 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000044.1</t>
+          <t>ItemData.Item.1000044</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>리피파이가 애정으로 한 알 한 알 손수 뭉친 진주빛 알갱이 펄 파우더. 사역마에게 사용하면 체력을 5 회복시켜준다.</t>
+          <t>더스트 펄</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -2278,12 +2278,12 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000061</t>
+          <t>ItemData.Item.1000044.1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>사역마 플러피 쿠션</t>
+          <t>리피파이가 애정으로 한 알 한 알 손수 뭉친 진주빛 알갱이 펄 파우더. 사역마에게 사용하면 체력을 5 회복시켜준다.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -2292,12 +2292,12 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000061.2</t>
+          <t>ItemData.Item.1000061</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>마법 같은 포근함으로 어떤 성실한 사역마도 잠들게 만드는 쿠션. 잠든 사역마는 달콤한 꿈을 꾸며 체력을 100 회복한다.</t>
+          <t>사역마 플러피 쿠션</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -2306,12 +2306,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000062</t>
+          <t>ItemData.Item.1000061.2</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>보송송 목도리</t>
+          <t>마법 같은 포근함으로 어떤 성실한 사역마도 잠들게 만드는 쿠션. 잠든 사역마는 달콤한 꿈을 꾸며 체력을 100 회복한다.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -2320,12 +2320,12 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000062.3</t>
+          <t>ItemData.Item.1000062</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>추운 날씨엔 사역마에게 따스한 목도리를 둘러주자. 찬바람에 소모된 체력을 즉시 100 회복할 수 있다.</t>
+          <t>보송송 목도리</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -2334,12 +2334,12 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000063</t>
+          <t>ItemData.Item.1000062.3</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>사역마용 실키 퍼프</t>
+          <t>추운 날씨엔 사역마에게 따스한 목도리를 둘러주자. 찬바람에 소모된 체력을 즉시 100 회복할 수 있다.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -2348,12 +2348,12 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000063.1</t>
+          <t>ItemData.Item.1000063</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>지쳐서 푸석해진 사역마를 순식간에 뽀송하게 되돌려주는 실키 퍼프.</t>
+          <t>사역마용 실키 퍼프</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -2362,12 +2362,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000045</t>
+          <t>ItemData.Item.1000063.1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>옐로우 허니 파우더</t>
+          <t>지쳐서 푸석해진 사역마를 순식간에 뽀송하게 되돌려주는 실키 퍼프.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -2376,12 +2376,12 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000045.1</t>
+          <t>ItemData.Item.1000045</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>정오의 햇살이 가장 진하게 고이는 한때를 곱게 빻아 담았다고 하는 노란빛깔의 파우더. 매듭을 풀면 온기가 새어나와 손끝이 먼저 따뜻해진다. 주머니에 매달린 태그에는 흐린 글씨로 '해가 지기 전에 쓸 것'이라 적혀 있지만, 잘 지켜지지 않는다.</t>
+          <t>옐로우 허니 파우더</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -2390,12 +2390,12 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000064</t>
+          <t>ItemData.Item.1000045.1</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>솜솜가루</t>
+          <t>정오의 햇살이 가장 진하게 고이는 한때를 곱게 빻아 담았다고 하는 노란빛깔의 파우더. 매듭을 풀면 온기가 새어나와 손끝이 먼저 따뜻해진다. 주머니에 매달린 태그에는 흐린 글씨로 '해가 지기 전에 쓸 것'이라 적혀 있지만, 잘 지켜지지 않는다.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -2404,12 +2404,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000064.2</t>
+          <t>ItemData.Item.1000064</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>홈베이킹에 쓰이는 가정용 솜사탕 재료. 솜사탕 가게에서 조금씩 얻을 수 있다?</t>
+          <t>솜솜가루</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -2418,12 +2418,12 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000065</t>
+          <t>ItemData.Item.1000064.2</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>솜솜 열매</t>
+          <t>홈베이킹에 쓰이는 가정용 솜사탕 재료. 솜사탕 가게에서 조금씩 얻을 수 있다?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2432,12 +2432,12 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000065.3</t>
+          <t>ItemData.Item.1000065</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>달달한 솜이 폭신하게 열린 솜솜 열매. 잘 심어 가꾸면 더 많은 솜사탕 재료를 얻을 수 있을 것이다.</t>
+          <t>솜솜 열매</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2446,12 +2446,12 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000066</t>
+          <t>ItemData.Item.1000065.3</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>푸른 꿈결정</t>
+          <t>달달한 솜이 폭신하게 열린 솜솜 열매. 잘 심어 가꾸면 더 많은 솜사탕 재료를 얻을 수 있을 것이다.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2460,12 +2460,12 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000066.4</t>
+          <t>ItemData.Item.1000066</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>홈베이킹용 솜솜가루가 달빛을 지나치게 흡수해 파랗게 물든 꿈결정. 때로는 실패가 성공보다 더 아름다운 결과를 가져오는 법이다.</t>
+          <t>푸른 꿈결정</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2474,12 +2474,12 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000067</t>
+          <t>ItemData.Item.1000066.4</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>솜사타</t>
+          <t>홈베이킹용 솜솜가루가 달빛을 지나치게 흡수해 파랗게 물든 꿈결정. 때로는 실패가 성공보다 더 아름다운 결과를 가져오는 법이다.</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2488,12 +2488,12 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000067.1</t>
+          <t>ItemData.Item.1000067</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>솜사타에 올라타! 바람처럼 빠르게 데려다줄거야!</t>
+          <t>솜사타</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2502,12 +2502,12 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000102</t>
+          <t>ItemData.Item.1000067.1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>페로페로 향수</t>
+          <t>솜사타에 올라타! 바람처럼 빠르게 데려다줄거야!</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2516,12 +2516,12 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000102.1</t>
+          <t>ItemData.Item.1000068</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>저항할 수 없는 묘한 향기를 풍겨 근처에 있는 사역마를 끌어당기는 미스테리한 향수. 매료된 사역마는 임시 계약을 맺어 하루 동안 당신을 돕는 데에 동의할 것이다.</t>
+          <t>페로페로 향수</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2530,12 +2530,12 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000103</t>
+          <t>ItemData.Item.1000068.1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>페로페로 향수</t>
+          <t>저항할 수 없는 묘한 향기를 풍겨 근처에 있는 사역마를 끌어당기는 미스테리한 향수. 매료된 사역마는 임시 계약을 맺어 하루 동안 당신을 돕는 데에 동의할 것이다.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2544,12 +2544,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000103.2</t>
+          <t>ItemData.Item.1000108</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>저항할 수 없는 묘한 향기를 풍겨 근처에 있는 사역마를 끌어당기는 미스테리한 향수. 매료된 사역마는 임시 계약을 맺어 하루 동안 당신을 돕는 데에 동의할 것이다.</t>
+          <t>A형 소환 마도서</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2558,12 +2558,12 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000104</t>
+          <t>ItemData.Item.1000108.2</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>페로페로 향수</t>
+          <t>설명 필요</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2572,12 +2572,12 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000104.3</t>
+          <t>ItemData.Item.1000109</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>저항할 수 없는 묘한 향기를 풍겨 근처에 있는 사역마를 끌어당기는 미스테리한 향수. 매료된 사역마는 임시 계약을 맺어 하루 동안 당신을 돕는 데에 동의할 것이다.</t>
+          <t>B형 소환 마도서</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2586,12 +2586,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000069</t>
+          <t>ItemData.Item.1000109.3</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>솜솜 보틀</t>
+          <t>설명 필요</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2600,12 +2600,12 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000069.1</t>
+          <t>ItemData.Item.1000110</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>달콤한 솜사탕을 집에서도 만들고 싶다면 솜솜 보틀이 필요할 것이다. 전용 용기가 솜사탕의 달콤함을 오래도록 지켜줄 테니까!</t>
+          <t>C형 소환 마도서</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2614,12 +2614,12 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000100</t>
+          <t>ItemData.Item.1000110.0</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>굿나잇 아이마스크</t>
+          <t>설명 필요</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2628,12 +2628,12 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000100.1</t>
+          <t>ItemData.Item.1000069</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>전설적인 선배 마법소녀들이 남긴 비밀 일지에 따르면, 푹 자고 일어나 맑아진 정신과 반짝이는 눈빛이야말로 마법을 성공시키는 진정한 비결! 마도구 진화 성공 확률을 10프로 높여주는 굿나잇 아이마스크.</t>
+          <t>솜솜 보틀</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2642,12 +2642,12 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000101</t>
+          <t>ItemData.Item.1000069.1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>폭닥폭닥 수면양말</t>
+          <t>달콤한 솜사탕을 집에서도 만들고 싶다면 솜솜 보틀이 필요할 것이다. 전용 용기가 솜사탕의 달콤함을 오래도록 지켜줄 테니까!</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2656,12 +2656,12 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ItemData.Item.1000101.2</t>
+          <t>ItemData.Item.1000100</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>체온을 높여주는 폭닥폭닥한 수면양말로, 마도구 합성 성공 확률을 5프로 높여준다. 한바탕 춤을 춰도 미끄러지지 않도록 내장된 발바닥 패드는 덤. 하루에 다섯 켤레까지 겹쳐서 착용할 수 있다?!</t>
+          <t>굿나잇 아이마스크</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2670,12 +2670,12 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000007</t>
+          <t>ItemData.Item.1000100.1</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>로딩 내용 어쩌고 저쩌고1</t>
+          <t>전설적인 선배 마법소녀들이 남긴 비밀 일지에 따르면, 푹 자고 일어나 맑아진 정신과 반짝이는 눈빛이야말로 마법을 성공시키는 진정한 비결! 마도구 진화 성공 확률을 10프로 높여주는 굿나잇 아이마스크.</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2684,12 +2684,12 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000008</t>
+          <t>ItemData.Item.1000101</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>로딩 내용 어쩌고 저쩌고2</t>
+          <t>폭닥폭닥 수면양말</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2698,12 +2698,12 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000027</t>
+          <t>ItemData.Item.1000101.2</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>솜사탕상점 로딩화면</t>
+          <t>체온을 높여주는 폭닥폭닥한 수면양말로, 마도구 합성 성공 확률을 5프로 높여준다. 한바탕 춤을 춰도 미끄러지지 않도록 내장된 발바닥 패드는 덤. 하루에 다섯 켤레까지 겹쳐서 착용할 수 있다?!</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
@@ -2712,12 +2712,12 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000028</t>
+          <t>LoadingData.Loading.1000007</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>파우더상점 로딩화면</t>
+          <t>로딩 내용 어쩌고 저쩌고1</t>
         </is>
       </c>
       <c r="C163" t="inlineStr"/>
@@ -2726,12 +2726,12 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>LoadingData.Loading.1000029</t>
+          <t>LoadingData.Loading.1000008</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>이불상점 로딩화면</t>
+          <t>로딩 내용 어쩌고 저쩌고2</t>
         </is>
       </c>
       <c r="C164" t="inlineStr"/>
@@ -2740,12 +2740,12 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>MapNpcData.MapNpcMenu.1000009.1</t>
+          <t>LoadingData.Loading.1000027</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>미니게임 시작</t>
+          <t>솜사탕상점 로딩화면</t>
         </is>
       </c>
       <c r="C165" t="inlineStr"/>
@@ -2754,12 +2754,12 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>MapNpcData.MapNpcMenu.1000030.1</t>
+          <t>LoadingData.Loading.1000028</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>말걸기</t>
+          <t>파우더상점 로딩화면</t>
         </is>
       </c>
       <c r="C166" t="inlineStr"/>
@@ -2768,12 +2768,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>MapNpcData.MapNpcMenu.1000078.1</t>
+          <t>LoadingData.Loading.1000029</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>말걸기</t>
+          <t>이불상점 로딩화면</t>
         </is>
       </c>
       <c r="C167" t="inlineStr"/>
@@ -2782,7 +2782,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>MapNpcData.MapStaticNpcMenu.1000031.1</t>
+          <t>MapNpcData.MapNpcMenu.1000009.1</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -2796,16 +2796,58 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>MapNpcData.MapStaticNpcMenu.1000084.1</t>
+          <t>MapNpcData.MapNpcMenu.1000030.1</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>미니게임 시작</t>
+          <t>말걸기</t>
         </is>
       </c>
       <c r="C169" t="inlineStr"/>
       <c r="D169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapNpcMenu.1000078.1</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>말걸기</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapStaticNpcMenu.1000031.1</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>미니게임 시작</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>MapNpcData.MapStaticNpcMenu.1000084.1</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>미니게임 시작</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
